--- a/reports/pdf_change_20260914.xlsx
+++ b/reports/pdf_change_20260914.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,659억   ·   현금 12억(0.3%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 3종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,523억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -879,7 +879,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,489억   ·   현금 43억(1.3%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,429억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -903,7 +903,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 40억(1.6%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,549억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -927,7 +927,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,974억   ·   현금 18억(0.9%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,944억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1044,7 +1044,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 1억(0.3%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1068,7 +1068,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억   ·   현금 4억(0.9%)      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 485억      당일 2026-09-14  vs  전영업일 2026-09-11      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
